--- a/data/trans_camb/IP16B03-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16B03-Edad-trans_camb.xlsx
@@ -802,17 +802,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,65</t>
+          <t>0,0; 57,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,24</t>
+          <t>0,0; 38,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,24</t>
+          <t>0,0; 38,3</t>
         </is>
       </c>
     </row>
@@ -878,17 +878,17 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 87,44</t>
+          <t>0,0; 134,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,84</t>
+          <t>0,0; 62,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,84</t>
+          <t>0,0; 62,4</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-50,46; 0,0</t>
+          <t>-51,48; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,0</t>
+          <t>-75,0; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,55</t>
+          <t>0,0; 40,44</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,88</t>
+          <t>0,0; 36,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-17,14; 8,71</t>
+          <t>-16,88; 8,69</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-16,8; 8,75</t>
+          <t>-17,86; 8,49</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-50,46; 0,0</t>
+          <t>-51,48; 0,0</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,0</t>
+          <t>-75,0; 0,0</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,99</t>
+          <t>0,0; 68,54</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,0</t>
+          <t>0,0; 56,86</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-17,67; 9,5</t>
+          <t>-16,93; 9,48</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-17,32; 9,55</t>
+          <t>-18,33; 9,28</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16B03-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP16B03-Edad-trans_camb.xlsx
@@ -656,7 +656,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-80,0; 0,0</t>
+          <t>-75,5; 0,0</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-80,0; 0,0</t>
+          <t>-75,5; 0,0</t>
         </is>
       </c>
     </row>
@@ -802,17 +802,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,27</t>
+          <t>0,0; 56,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,3</t>
+          <t>0,0; 37,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,3</t>
+          <t>0,0; 37,26</t>
         </is>
       </c>
     </row>
@@ -878,17 +878,17 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 134,01</t>
+          <t>0,0; 130,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,4</t>
+          <t>0,0; 59,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,4</t>
+          <t>0,0; 59,55</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-51,48; 0,0</t>
+          <t>-44,32; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1265,22 +1265,22 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,44</t>
+          <t>0,0; 36,99</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,2</t>
+          <t>0,0; 37,63</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-16,88; 8,69</t>
+          <t>-21,51; 8,79</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-17,86; 8,49</t>
+          <t>-17,23; 8,77</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-51,48; 0,0</t>
+          <t>-44,32; 0,0</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1341,22 +1341,22 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,54</t>
+          <t>0,0; 58,72</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,86</t>
+          <t>0,0; 60,33</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-16,93; 9,48</t>
+          <t>-21,64; 9,57</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-18,33; 9,28</t>
+          <t>-17,54; 9,6</t>
         </is>
       </c>
     </row>
